--- a/(枠)◯年度一式/管理月報/管理月報12.xlsx
+++ b/(枠)◯年度一式/管理月報/管理月報12.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\管理月報\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\管理月報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AAD68DE-F226-4F09-8983-2F6E067A0593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DF0DBD-352A-482F-89FD-48089528F1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="465" windowWidth="15750" windowHeight="15480" tabRatio="848" activeTab="5" xr2:uid="{82636C2E-B737-47B8-9F9F-6B496266DD4F}"/>
+    <workbookView xWindow="1170" yWindow="0" windowWidth="16215" windowHeight="15480" tabRatio="848" xr2:uid="{82636C2E-B737-47B8-9F9F-6B496266DD4F}"/>
   </bookViews>
   <sheets>
     <sheet name="A-1" sheetId="1" r:id="rId1"/>
@@ -3304,9 +3304,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -3324,6 +3321,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -3632,16 +3632,38 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="A-1"/>
+      <sheetName val="A-2"/>
+      <sheetName val="B-1"/>
+      <sheetName val="収集（全般）"/>
+      <sheetName val="可燃"/>
+      <sheetName val="不燃・木くず・海岸清掃"/>
+      <sheetName val="ビン類"/>
+      <sheetName val="缶類"/>
+      <sheetName val="ペットボトル"/>
+      <sheetName val="紙類"/>
+      <sheetName val="粗大"/>
+      <sheetName val="産廃水産・医療・汚泥"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>8</v>
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4050,8 +4072,8 @@
         <v>34</v>
       </c>
       <c r="B9" s="151" t="str">
-        <f>"(令和"&amp;[1]Sheet1!$C$2&amp;"年12月)"</f>
-        <v>(令和8年12月)</v>
+        <f>"("&amp;TEXT(DATE('[1]A-1'!$E$9, 12, 1), "ggge年mm月")&amp;")"</f>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -5321,7 +5343,7 @@
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -6837,7 +6859,7 @@
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -8546,7 +8568,7 @@
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -8567,13 +8589,13 @@
       <c r="I10" s="191"/>
       <c r="J10" s="191"/>
       <c r="K10" s="192"/>
-      <c r="L10" s="154" t="s">
+      <c r="L10" s="160" t="s">
         <v>161</v>
       </c>
-      <c r="M10" s="154"/>
-      <c r="N10" s="154"/>
-      <c r="O10" s="154"/>
-      <c r="P10" s="154"/>
+      <c r="M10" s="160"/>
+      <c r="N10" s="160"/>
+      <c r="O10" s="160"/>
+      <c r="P10" s="160"/>
       <c r="Q10" s="190" t="s">
         <v>181</v>
       </c>
@@ -10067,63 +10089,63 @@
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="2"/>
-      <c r="F5" s="154" t="s">
+      <c r="F5" s="160" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154" t="s">
+      <c r="G5" s="160"/>
+      <c r="H5" s="160" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="154"/>
-      <c r="J5" s="154" t="s">
+      <c r="I5" s="160"/>
+      <c r="J5" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="154"/>
-      <c r="L5" s="154" t="s">
+      <c r="K5" s="160"/>
+      <c r="L5" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="154"/>
-      <c r="N5" s="154"/>
+      <c r="M5" s="160"/>
+      <c r="N5" s="160"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="F6" s="154" t="s">
+      <c r="F6" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="154"/>
-      <c r="H6" s="155" t="s">
+      <c r="G6" s="160"/>
+      <c r="H6" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="157"/>
-      <c r="J6" s="154" t="s">
+      <c r="I6" s="156"/>
+      <c r="J6" s="160" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="154"/>
-      <c r="L6" s="154" t="s">
+      <c r="K6" s="160"/>
+      <c r="L6" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="154"/>
-      <c r="N6" s="154"/>
+      <c r="M6" s="160"/>
+      <c r="N6" s="160"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="F7" s="154" t="s">
+      <c r="F7" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="154"/>
-      <c r="H7" s="154" t="s">
+      <c r="G7" s="160"/>
+      <c r="H7" s="160" t="s">
         <v>196</v>
       </c>
-      <c r="I7" s="154"/>
-      <c r="J7" s="154" t="s">
+      <c r="I7" s="160"/>
+      <c r="J7" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="154"/>
-      <c r="L7" s="154" t="s">
+      <c r="K7" s="160"/>
+      <c r="L7" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="154"/>
-      <c r="N7" s="154"/>
+      <c r="M7" s="160"/>
+      <c r="N7" s="160"/>
     </row>
     <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
@@ -10143,7 +10165,7 @@
       </c>
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -10158,14 +10180,14 @@
       <c r="C10" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="155" t="s">
+      <c r="D10" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="156"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="157"/>
+      <c r="E10" s="155"/>
+      <c r="F10" s="155"/>
+      <c r="G10" s="155"/>
+      <c r="H10" s="155"/>
+      <c r="I10" s="156"/>
       <c r="J10" s="39" t="s">
         <v>13</v>
       </c>
@@ -10175,10 +10197,10 @@
       <c r="L10" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="M10" s="155" t="s">
+      <c r="M10" s="154" t="s">
         <v>42</v>
       </c>
-      <c r="N10" s="157"/>
+      <c r="N10" s="156"/>
     </row>
     <row r="11" spans="1:16" s="40" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="46"/>
@@ -10188,16 +10210,16 @@
       <c r="C11" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="155" t="s">
+      <c r="D11" s="154" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="156"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="158" t="s">
+      <c r="E11" s="155"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="157" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="159"/>
-      <c r="I11" s="160"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="159"/>
       <c r="J11" s="41" t="s">
         <v>14</v>
       </c>
@@ -11318,7 +11340,7 @@
       </c>
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -13405,7 +13427,7 @@
     <row r="9" spans="1:31" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="177" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="177"/>
       <c r="D9" s="178"/>
@@ -15451,7 +15473,7 @@
     <row r="9" spans="1:22" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="185" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="185"/>
       <c r="D9" s="186"/>
@@ -16967,7 +16989,7 @@
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -18659,7 +18681,7 @@
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -20173,7 +20195,7 @@
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>
@@ -21687,7 +21709,7 @@
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="151" t="str">
         <f>'A-1'!B9:D9</f>
-        <v>(令和8年12月)</v>
+        <v>(令和9年12月)</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="152"/>

--- a/(枠)◯年度一式/管理月報/管理月報12.xlsx
+++ b/(枠)◯年度一式/管理月報/管理月報12.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\管理月報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DF0DBD-352A-482F-89FD-48089528F1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA56BC25-224D-4A94-A731-67B74B21FC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="0" windowWidth="16215" windowHeight="15480" tabRatio="848" xr2:uid="{82636C2E-B737-47B8-9F9F-6B496266DD4F}"/>
+    <workbookView xWindow="7995" yWindow="765" windowWidth="18615" windowHeight="14715" tabRatio="848" xr2:uid="{82636C2E-B737-47B8-9F9F-6B496266DD4F}"/>
   </bookViews>
   <sheets>
     <sheet name="A-1" sheetId="1" r:id="rId1"/>
@@ -3274,18 +3274,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -3302,6 +3290,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3322,8 +3325,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -3343,27 +3361,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3373,12 +3370,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3386,6 +3377,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3970,89 +3970,89 @@
     <row r="2" spans="1:18" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:18" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="4" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="144"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="144"/>
-      <c r="J4" s="144"/>
-      <c r="K4" s="144"/>
-      <c r="L4" s="144"/>
-      <c r="M4" s="144"/>
-      <c r="N4" s="144"/>
-      <c r="O4" s="144"/>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
-      <c r="R4" s="144"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="151"/>
+      <c r="M4" s="151"/>
+      <c r="N4" s="151"/>
+      <c r="O4" s="151"/>
+      <c r="P4" s="151"/>
+      <c r="Q4" s="151"/>
+      <c r="R4" s="151"/>
     </row>
     <row r="5" spans="1:18" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
-      <c r="I5" s="145" t="s">
+      <c r="I5" s="150" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145" t="s">
+      <c r="J5" s="150"/>
+      <c r="K5" s="150" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145" t="s">
+      <c r="L5" s="150"/>
+      <c r="M5" s="150"/>
+      <c r="N5" s="150"/>
+      <c r="O5" s="150" t="s">
         <v>69</v>
       </c>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="146" t="s">
+      <c r="P5" s="150"/>
+      <c r="Q5" s="152" t="s">
         <v>26</v>
       </c>
-      <c r="R5" s="147"/>
+      <c r="R5" s="153"/>
     </row>
     <row r="6" spans="1:18" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="I6" s="145" t="s">
+      <c r="I6" s="150" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="145"/>
-      <c r="K6" s="145" t="s">
+      <c r="J6" s="150"/>
+      <c r="K6" s="150" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="145"/>
-      <c r="M6" s="145"/>
-      <c r="N6" s="145"/>
-      <c r="O6" s="145" t="s">
+      <c r="L6" s="150"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="150"/>
+      <c r="O6" s="150" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="145"/>
-      <c r="Q6" s="145" t="s">
+      <c r="P6" s="150"/>
+      <c r="Q6" s="150" t="s">
         <v>27</v>
       </c>
-      <c r="R6" s="145"/>
+      <c r="R6" s="150"/>
     </row>
     <row r="7" spans="1:18" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="I7" s="145" t="s">
+      <c r="I7" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="145"/>
-      <c r="K7" s="153" t="s">
+      <c r="J7" s="150"/>
+      <c r="K7" s="149" t="s">
         <v>196</v>
       </c>
-      <c r="L7" s="145"/>
-      <c r="M7" s="145"/>
-      <c r="N7" s="145"/>
-      <c r="O7" s="145" t="s">
+      <c r="L7" s="150"/>
+      <c r="M7" s="150"/>
+      <c r="N7" s="150"/>
+      <c r="O7" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145" t="s">
+      <c r="P7" s="150"/>
+      <c r="Q7" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="145"/>
+      <c r="R7" s="150"/>
     </row>
     <row r="8" spans="1:18" s="3" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
@@ -4071,12 +4071,12 @@
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>"("&amp;TEXT(DATE('[1]A-1'!$E$9, 12, 1), "ggge年mm月")&amp;")"</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
       <c r="E9" s="90"/>
     </row>
     <row r="10" spans="1:18" s="38" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4119,13 +4119,13 @@
       <c r="M10" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="N10" s="148" t="s">
+      <c r="N10" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="149"/>
-      <c r="P10" s="149"/>
-      <c r="Q10" s="149"/>
-      <c r="R10" s="150"/>
+      <c r="O10" s="145"/>
+      <c r="P10" s="145"/>
+      <c r="Q10" s="145"/>
+      <c r="R10" s="146"/>
     </row>
     <row r="11" spans="1:18" s="38" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="94"/>
@@ -5260,12 +5260,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="N10:R10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
     <mergeCell ref="A4:R4"/>
     <mergeCell ref="Q6:R6"/>
     <mergeCell ref="Q5:R5"/>
@@ -5275,6 +5269,12 @@
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="K5:N5"/>
     <mergeCell ref="K6:N6"/>
+    <mergeCell ref="N10:R10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="A13:A43">
@@ -5341,12 +5341,12 @@
     <row r="7" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="103"/>
@@ -6857,15 +6857,15 @@
     <row r="7" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
-      <c r="G9" s="151"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
+      <c r="G9" s="147"/>
+      <c r="H9" s="147"/>
+      <c r="I9" s="148"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="103"/>
@@ -8566,12 +8566,12 @@
     <row r="7" spans="1:24" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:24" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="103"/>
@@ -8589,13 +8589,13 @@
       <c r="I10" s="191"/>
       <c r="J10" s="191"/>
       <c r="K10" s="192"/>
-      <c r="L10" s="160" t="s">
+      <c r="L10" s="154" t="s">
         <v>161</v>
       </c>
-      <c r="M10" s="160"/>
-      <c r="N10" s="160"/>
-      <c r="O10" s="160"/>
-      <c r="P10" s="160"/>
+      <c r="M10" s="154"/>
+      <c r="N10" s="154"/>
+      <c r="O10" s="154"/>
+      <c r="P10" s="154"/>
       <c r="Q10" s="190" t="s">
         <v>181</v>
       </c>
@@ -10051,22 +10051,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="25.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="151" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
       <c r="O1" s="99"/>
       <c r="P1" s="99"/>
     </row>
@@ -10089,63 +10089,63 @@
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="2"/>
-      <c r="F5" s="160" t="s">
+      <c r="F5" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="160" t="s">
+      <c r="G5" s="154"/>
+      <c r="H5" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="160"/>
-      <c r="J5" s="160" t="s">
+      <c r="I5" s="154"/>
+      <c r="J5" s="154" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="160"/>
-      <c r="L5" s="160" t="s">
+      <c r="K5" s="154"/>
+      <c r="L5" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="160"/>
-      <c r="N5" s="160"/>
+      <c r="M5" s="154"/>
+      <c r="N5" s="154"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
-      <c r="F6" s="160" t="s">
+      <c r="F6" s="154" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="160"/>
-      <c r="H6" s="154" t="s">
+      <c r="G6" s="154"/>
+      <c r="H6" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="156"/>
-      <c r="J6" s="160" t="s">
+      <c r="I6" s="157"/>
+      <c r="J6" s="154" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="160"/>
-      <c r="L6" s="160" t="s">
+      <c r="K6" s="154"/>
+      <c r="L6" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="160"/>
-      <c r="N6" s="160"/>
+      <c r="M6" s="154"/>
+      <c r="N6" s="154"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="2"/>
-      <c r="F7" s="160" t="s">
+      <c r="F7" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160" t="s">
+      <c r="G7" s="154"/>
+      <c r="H7" s="154" t="s">
         <v>196</v>
       </c>
-      <c r="I7" s="160"/>
-      <c r="J7" s="160" t="s">
+      <c r="I7" s="154"/>
+      <c r="J7" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="160"/>
-      <c r="L7" s="160" t="s">
+      <c r="K7" s="154"/>
+      <c r="L7" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="160"/>
-      <c r="N7" s="160"/>
+      <c r="M7" s="154"/>
+      <c r="N7" s="154"/>
     </row>
     <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
@@ -10163,12 +10163,12 @@
       <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
     </row>
     <row r="10" spans="1:16" s="40" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="45" t="s">
@@ -10180,14 +10180,14 @@
       <c r="C10" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="154" t="s">
+      <c r="D10" s="155" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="155"/>
-      <c r="F10" s="155"/>
-      <c r="G10" s="155"/>
-      <c r="H10" s="155"/>
-      <c r="I10" s="156"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="156"/>
+      <c r="I10" s="157"/>
       <c r="J10" s="39" t="s">
         <v>13</v>
       </c>
@@ -10197,10 +10197,10 @@
       <c r="L10" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="M10" s="154" t="s">
+      <c r="M10" s="155" t="s">
         <v>42</v>
       </c>
-      <c r="N10" s="156"/>
+      <c r="N10" s="157"/>
     </row>
     <row r="11" spans="1:16" s="40" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="46"/>
@@ -10210,16 +10210,16 @@
       <c r="C11" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="154" t="s">
+      <c r="D11" s="155" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="155"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="157" t="s">
+      <c r="E11" s="156"/>
+      <c r="F11" s="157"/>
+      <c r="G11" s="158" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="158"/>
-      <c r="I11" s="159"/>
+      <c r="H11" s="159"/>
+      <c r="I11" s="160"/>
       <c r="J11" s="41" t="s">
         <v>14</v>
       </c>
@@ -11119,6 +11119,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="L7:N7"/>
     <mergeCell ref="A1:N1"/>
@@ -11132,11 +11137,6 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="A13:A43">
@@ -11172,149 +11172,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="101" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="167" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="161"/>
-      <c r="H1" s="161"/>
-      <c r="I1" s="161"/>
-      <c r="J1" s="161"/>
-      <c r="K1" s="161"/>
-      <c r="L1" s="161"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
-      <c r="R1" s="161"/>
-      <c r="S1" s="161"/>
-      <c r="T1" s="161"/>
-      <c r="U1" s="161"/>
-      <c r="V1" s="161"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="167"/>
+      <c r="N1" s="167"/>
+      <c r="O1" s="167"/>
+      <c r="P1" s="167"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="167"/>
+      <c r="S1" s="167"/>
+      <c r="T1" s="167"/>
+      <c r="U1" s="167"/>
+      <c r="V1" s="167"/>
     </row>
     <row r="2" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H2" s="167" t="s">
+      <c r="H2" s="161" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="168"/>
-      <c r="J2" s="169" t="s">
+      <c r="I2" s="162"/>
+      <c r="J2" s="163" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="170"/>
-      <c r="L2" s="171"/>
-      <c r="M2" s="167" t="s">
+      <c r="K2" s="164"/>
+      <c r="L2" s="165"/>
+      <c r="M2" s="161" t="s">
         <v>75</v>
       </c>
-      <c r="N2" s="172"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169" t="s">
+      <c r="N2" s="166"/>
+      <c r="O2" s="162"/>
+      <c r="P2" s="163" t="s">
         <v>195</v>
       </c>
-      <c r="Q2" s="170"/>
-      <c r="R2" s="170"/>
-      <c r="S2" s="170"/>
-      <c r="T2" s="171"/>
+      <c r="Q2" s="164"/>
+      <c r="R2" s="164"/>
+      <c r="S2" s="164"/>
+      <c r="T2" s="165"/>
     </row>
     <row r="3" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H3" s="167" t="s">
+      <c r="H3" s="161" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="168"/>
-      <c r="J3" s="169" t="s">
+      <c r="I3" s="162"/>
+      <c r="J3" s="163" t="s">
         <v>173</v>
       </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="171"/>
-      <c r="M3" s="167" t="s">
+      <c r="K3" s="164"/>
+      <c r="L3" s="165"/>
+      <c r="M3" s="161" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="172"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169" t="s">
+      <c r="N3" s="166"/>
+      <c r="O3" s="162"/>
+      <c r="P3" s="163" t="s">
         <v>160</v>
       </c>
-      <c r="Q3" s="170"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="170"/>
-      <c r="T3" s="171"/>
+      <c r="Q3" s="164"/>
+      <c r="R3" s="164"/>
+      <c r="S3" s="164"/>
+      <c r="T3" s="165"/>
     </row>
     <row r="4" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="161" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="168"/>
-      <c r="J4" s="169" t="s">
+      <c r="I4" s="162"/>
+      <c r="J4" s="163" t="s">
         <v>174</v>
       </c>
-      <c r="K4" s="170"/>
-      <c r="L4" s="171"/>
-      <c r="M4" s="167" t="s">
+      <c r="K4" s="164"/>
+      <c r="L4" s="165"/>
+      <c r="M4" s="161" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="172"/>
-      <c r="O4" s="168"/>
-      <c r="P4" s="169" t="s">
+      <c r="N4" s="166"/>
+      <c r="O4" s="162"/>
+      <c r="P4" s="163" t="s">
         <v>175</v>
       </c>
-      <c r="Q4" s="170"/>
-      <c r="R4" s="170"/>
-      <c r="S4" s="170"/>
-      <c r="T4" s="171"/>
+      <c r="Q4" s="164"/>
+      <c r="R4" s="164"/>
+      <c r="S4" s="164"/>
+      <c r="T4" s="165"/>
     </row>
     <row r="5" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H5" s="167" t="s">
+      <c r="H5" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="168"/>
-      <c r="J5" s="169" t="s">
+      <c r="I5" s="162"/>
+      <c r="J5" s="163" t="s">
         <v>176</v>
       </c>
-      <c r="K5" s="170"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="167" t="s">
+      <c r="K5" s="164"/>
+      <c r="L5" s="165"/>
+      <c r="M5" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="N5" s="168"/>
+      <c r="N5" s="162"/>
       <c r="O5" s="59" t="s">
         <v>177</v>
       </c>
-      <c r="P5" s="169" t="s">
+      <c r="P5" s="163" t="s">
         <v>171</v>
       </c>
-      <c r="Q5" s="170"/>
-      <c r="R5" s="170"/>
-      <c r="S5" s="170"/>
-      <c r="T5" s="171"/>
+      <c r="Q5" s="164"/>
+      <c r="R5" s="164"/>
+      <c r="S5" s="164"/>
+      <c r="T5" s="165"/>
     </row>
     <row r="6" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H6" s="167" t="s">
+      <c r="H6" s="161" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="168"/>
-      <c r="J6" s="167" t="s">
+      <c r="I6" s="162"/>
+      <c r="J6" s="161" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="172"/>
-      <c r="L6" s="168"/>
-      <c r="M6" s="167" t="s">
+      <c r="K6" s="166"/>
+      <c r="L6" s="162"/>
+      <c r="M6" s="161" t="s">
         <v>80</v>
       </c>
-      <c r="N6" s="168"/>
+      <c r="N6" s="162"/>
       <c r="O6" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="P6" s="169" t="s">
+      <c r="P6" s="163" t="s">
         <v>172</v>
       </c>
-      <c r="Q6" s="170"/>
-      <c r="R6" s="170"/>
-      <c r="S6" s="170"/>
-      <c r="T6" s="171"/>
+      <c r="Q6" s="164"/>
+      <c r="R6" s="164"/>
+      <c r="S6" s="164"/>
+      <c r="T6" s="165"/>
     </row>
     <row r="7" spans="1:22" s="44" customFormat="1" ht="11.25" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="P7" s="105"/>
@@ -11338,12 +11338,12 @@
       <c r="A9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -11353,28 +11353,28 @@
         <v>0</v>
       </c>
       <c r="B10" s="75"/>
-      <c r="C10" s="162" t="s">
+      <c r="C10" s="168" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="163"/>
-      <c r="E10" s="163"/>
-      <c r="F10" s="163"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
       <c r="I10" s="75"/>
-      <c r="J10" s="164" t="s">
+      <c r="J10" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="K10" s="165"/>
-      <c r="L10" s="165"/>
-      <c r="M10" s="165"/>
-      <c r="N10" s="165"/>
-      <c r="O10" s="165"/>
-      <c r="P10" s="165"/>
-      <c r="Q10" s="165"/>
-      <c r="R10" s="165"/>
-      <c r="S10" s="165"/>
-      <c r="T10" s="166"/>
+      <c r="K10" s="171"/>
+      <c r="L10" s="171"/>
+      <c r="M10" s="171"/>
+      <c r="N10" s="171"/>
+      <c r="O10" s="171"/>
+      <c r="P10" s="171"/>
+      <c r="Q10" s="171"/>
+      <c r="R10" s="171"/>
+      <c r="S10" s="171"/>
+      <c r="T10" s="172"/>
     </row>
     <row r="11" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="77"/>
@@ -11408,19 +11408,19 @@
       <c r="K11" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="164" t="s">
+      <c r="L11" s="170" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="165"/>
-      <c r="N11" s="165"/>
-      <c r="O11" s="165"/>
-      <c r="P11" s="164" t="s">
+      <c r="M11" s="171"/>
+      <c r="N11" s="171"/>
+      <c r="O11" s="171"/>
+      <c r="P11" s="170" t="s">
         <v>63</v>
       </c>
-      <c r="Q11" s="165"/>
-      <c r="R11" s="165"/>
-      <c r="S11" s="165"/>
-      <c r="T11" s="166"/>
+      <c r="Q11" s="171"/>
+      <c r="R11" s="171"/>
+      <c r="S11" s="171"/>
+      <c r="T11" s="172"/>
     </row>
     <row r="12" spans="1:22" s="44" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="77"/>
@@ -13325,16 +13325,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="P3:T3"/>
-    <mergeCell ref="P4:T4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L6"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="B9:D9"/>
@@ -13351,6 +13341,16 @@
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="M4:O4"/>
     <mergeCell ref="M5:N5"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="M6:N6"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="A14:A44">
@@ -13383,39 +13383,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="179" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
-      <c r="O1" s="173"/>
-      <c r="P1" s="173"/>
-      <c r="Q1" s="173"/>
-      <c r="R1" s="173"/>
-      <c r="S1" s="173"/>
-      <c r="T1" s="173"/>
-      <c r="U1" s="173"/>
-      <c r="V1" s="173"/>
-      <c r="W1" s="173"/>
-      <c r="X1" s="173"/>
-      <c r="Y1" s="173"/>
-      <c r="Z1" s="173"/>
-      <c r="AA1" s="173"/>
-      <c r="AB1" s="173"/>
-      <c r="AC1" s="173"/>
-      <c r="AD1" s="173"/>
-      <c r="AE1" s="173"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
+      <c r="M1" s="179"/>
+      <c r="N1" s="179"/>
+      <c r="O1" s="179"/>
+      <c r="P1" s="179"/>
+      <c r="Q1" s="179"/>
+      <c r="R1" s="179"/>
+      <c r="S1" s="179"/>
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="179"/>
+      <c r="AA1" s="179"/>
+      <c r="AB1" s="179"/>
+      <c r="AC1" s="179"/>
+      <c r="AD1" s="179"/>
+      <c r="AE1" s="179"/>
     </row>
     <row r="2" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -13425,104 +13425,104 @@
     <row r="7" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:31" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:31" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="177" t="str">
+      <c r="B9" s="180" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="177"/>
-      <c r="D9" s="178"/>
+      <c r="C9" s="180"/>
+      <c r="D9" s="181"/>
     </row>
     <row r="10" spans="1:31" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="109"/>
-      <c r="B10" s="174" t="s">
+      <c r="B10" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="175"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="174" t="s">
+      <c r="C10" s="174"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="175"/>
+      <c r="G10" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="175"/>
-      <c r="K10" s="176"/>
-      <c r="L10" s="174" t="s">
+      <c r="H10" s="174"/>
+      <c r="I10" s="174"/>
+      <c r="J10" s="174"/>
+      <c r="K10" s="175"/>
+      <c r="L10" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="175"/>
-      <c r="N10" s="175"/>
-      <c r="O10" s="175"/>
-      <c r="P10" s="176"/>
-      <c r="Q10" s="174" t="s">
+      <c r="M10" s="174"/>
+      <c r="N10" s="174"/>
+      <c r="O10" s="174"/>
+      <c r="P10" s="175"/>
+      <c r="Q10" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="R10" s="175"/>
-      <c r="S10" s="175"/>
-      <c r="T10" s="175"/>
-      <c r="U10" s="176"/>
-      <c r="V10" s="174" t="s">
+      <c r="R10" s="174"/>
+      <c r="S10" s="174"/>
+      <c r="T10" s="174"/>
+      <c r="U10" s="175"/>
+      <c r="V10" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="W10" s="175"/>
-      <c r="X10" s="175"/>
-      <c r="Y10" s="175"/>
-      <c r="Z10" s="176"/>
-      <c r="AA10" s="174" t="s">
+      <c r="W10" s="174"/>
+      <c r="X10" s="174"/>
+      <c r="Y10" s="174"/>
+      <c r="Z10" s="175"/>
+      <c r="AA10" s="173" t="s">
         <v>82</v>
       </c>
-      <c r="AB10" s="175"/>
-      <c r="AC10" s="175"/>
-      <c r="AD10" s="175"/>
-      <c r="AE10" s="176"/>
+      <c r="AB10" s="174"/>
+      <c r="AC10" s="174"/>
+      <c r="AD10" s="174"/>
+      <c r="AE10" s="175"/>
     </row>
     <row r="11" spans="1:31" s="107" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="174" t="s">
+      <c r="B11" s="173" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="175"/>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="176"/>
-      <c r="G11" s="174" t="s">
+      <c r="C11" s="174"/>
+      <c r="D11" s="174"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="173" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
-      <c r="J11" s="175"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="174" t="s">
+      <c r="H11" s="174"/>
+      <c r="I11" s="174"/>
+      <c r="J11" s="174"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="173" t="s">
         <v>137</v>
       </c>
-      <c r="M11" s="175"/>
-      <c r="N11" s="175"/>
-      <c r="O11" s="175"/>
-      <c r="P11" s="176"/>
-      <c r="Q11" s="174" t="s">
+      <c r="M11" s="174"/>
+      <c r="N11" s="174"/>
+      <c r="O11" s="174"/>
+      <c r="P11" s="175"/>
+      <c r="Q11" s="173" t="s">
         <v>128</v>
       </c>
-      <c r="R11" s="175"/>
-      <c r="S11" s="175"/>
-      <c r="T11" s="175"/>
-      <c r="U11" s="176"/>
-      <c r="V11" s="179" t="s">
+      <c r="R11" s="174"/>
+      <c r="S11" s="174"/>
+      <c r="T11" s="174"/>
+      <c r="U11" s="175"/>
+      <c r="V11" s="176" t="s">
         <v>189</v>
       </c>
-      <c r="W11" s="180"/>
-      <c r="X11" s="180"/>
-      <c r="Y11" s="180"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="174" t="s">
+      <c r="W11" s="177"/>
+      <c r="X11" s="177"/>
+      <c r="Y11" s="177"/>
+      <c r="Z11" s="178"/>
+      <c r="AA11" s="173" t="s">
         <v>136</v>
       </c>
-      <c r="AB11" s="175"/>
-      <c r="AC11" s="175"/>
-      <c r="AD11" s="175"/>
-      <c r="AE11" s="176"/>
+      <c r="AB11" s="174"/>
+      <c r="AC11" s="174"/>
+      <c r="AD11" s="174"/>
+      <c r="AE11" s="175"/>
     </row>
     <row r="12" spans="1:31" s="113" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="111"/>
@@ -15387,12 +15387,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="L11:P11"/>
-    <mergeCell ref="V11:Z11"/>
-    <mergeCell ref="AA11:AE11"/>
-    <mergeCell ref="Q11:U11"/>
-    <mergeCell ref="G11:K11"/>
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="L10:P10"/>
@@ -15401,6 +15395,12 @@
     <mergeCell ref="Q10:U10"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="G10:K10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="L11:P11"/>
+    <mergeCell ref="V11:Z11"/>
+    <mergeCell ref="AA11:AE11"/>
+    <mergeCell ref="Q11:U11"/>
+    <mergeCell ref="G11:K11"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="A13:A43">
@@ -15438,30 +15438,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.15">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="179" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="173"/>
-      <c r="N1" s="173"/>
-      <c r="O1" s="173"/>
-      <c r="P1" s="173"/>
-      <c r="Q1" s="173"/>
-      <c r="R1" s="173"/>
-      <c r="S1" s="173"/>
-      <c r="T1" s="173"/>
-      <c r="U1" s="173"/>
-      <c r="V1" s="173"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
+      <c r="M1" s="179"/>
+      <c r="N1" s="179"/>
+      <c r="O1" s="179"/>
+      <c r="P1" s="179"/>
+      <c r="Q1" s="179"/>
+      <c r="R1" s="179"/>
+      <c r="S1" s="179"/>
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
     </row>
     <row r="2" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -16987,12 +16987,12 @@
     <row r="7" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:26" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="103"/>
@@ -18679,12 +18679,12 @@
     <row r="7" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="103"/>
@@ -20193,12 +20193,12 @@
     <row r="7" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="103"/>
@@ -21707,12 +21707,12 @@
     <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.15"/>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="151" t="str">
+      <c r="B9" s="147" t="str">
         <f>'A-1'!B9:D9</f>
         <v>(令和9年12月)</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="103"/>
